--- a/resources/reselling/files/reselling-basics-sourcing-scorecard.xlsx
+++ b/resources/reselling/files/reselling-basics-sourcing-scorecard.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,9 +139,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -517,8 +514,8 @@
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sourcing comp check — one honest price (Basics, ch3)</t>
         </is>
@@ -651,7 +648,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
+    <row r="20">
       <c r="A20" s="11">
         <f>IF(B15&lt;3,"WALK — fewer than 3 valid comps. Not enough evidence: broaden the search or pass.","USE $"&amp;TEXT(B17,"0")&amp;" as your conservative sale price — carry it to the deal-sheet calculator.")</f>
         <v/>
@@ -666,9 +663,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
